--- a/data/Alamance Detailed Inventory On Hand 8-3-2026.xlsx
+++ b/data/Alamance Detailed Inventory On Hand 8-3-2026.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\toneil\AppData\Local\Microsoft\Windows\INetCache\Content.Outlook\D80LZKFS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://alamancefoods-my.sharepoint.com/personal/balapradeepkonda_alamancefoods_com/Documents/Documents/GitHub/Bala_Can_SupplyChain/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B0C33BC-1C9D-4F63-8932-33D3A55D6232}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="13_ncr:1_{3B0C33BC-1C9D-4F63-8932-33D3A55D6232}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1479D5D5-59C7-470B-B49C-7066D106407B}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{07513E19-67B5-4E50-873A-1F50CD4CBFF8}"/>
+    <workbookView xWindow="11244" yWindow="-17472" windowWidth="30936" windowHeight="16776" xr2:uid="{07513E19-67B5-4E50-873A-1F50CD4CBFF8}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -835,23 +835,25 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1DC00A56-8C57-46B1-B284-9AB06DC2753F}">
   <dimension ref="A1:R116"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="22.42578125" customWidth="1"/>
-    <col min="2" max="2" width="17.7109375" hidden="1" customWidth="1"/>
-    <col min="3" max="3" width="50.140625" customWidth="1"/>
-    <col min="4" max="5" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.85546875" customWidth="1"/>
-    <col min="7" max="7" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="12" max="16" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="17.7109375" customWidth="1"/>
+    <col min="1" max="1" width="22.44140625" customWidth="1"/>
+    <col min="2" max="2" width="17.6640625" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="50.109375" customWidth="1"/>
+    <col min="4" max="5" width="10.5546875" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="11.88671875" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="9.5546875" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="10.5546875" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="11.5546875" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="9.5546875" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="11.5546875" hidden="1" customWidth="1"/>
+    <col min="12" max="13" width="13.33203125" hidden="1" customWidth="1"/>
+    <col min="14" max="14" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="13.33203125" customWidth="1"/>
+    <col min="17" max="18" width="17.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
       <c r="C1" t="s">
         <v>0</v>
       </c>
@@ -859,7 +861,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
       <c r="D2" t="s">
         <v>2</v>
       </c>
@@ -900,7 +902,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
       <c r="C3" t="s">
         <v>7</v>
       </c>
@@ -935,7 +937,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>125</v>
       </c>
@@ -991,7 +993,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>12054</v>
       </c>
@@ -1028,7 +1030,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>12174</v>
       </c>
@@ -1065,7 +1067,7 @@
         <v>114000</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
         <v>12175</v>
       </c>
@@ -1104,7 +1106,7 @@
         <v>228000</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>12016</v>
       </c>
@@ -1137,7 +1139,7 @@
       <c r="Q8" s="1"/>
       <c r="R8" s="1"/>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>12398</v>
       </c>
@@ -1170,7 +1172,7 @@
       <c r="Q9" s="1"/>
       <c r="R9" s="1"/>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>12324</v>
       </c>
@@ -1203,7 +1205,7 @@
       <c r="Q10" s="1"/>
       <c r="R10" s="1"/>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>12362</v>
       </c>
@@ -1236,7 +1238,7 @@
       <c r="Q11" s="1"/>
       <c r="R11" s="1"/>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>12250</v>
       </c>
@@ -1269,7 +1271,7 @@
       <c r="Q12" s="1"/>
       <c r="R12" s="1"/>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>12252</v>
       </c>
@@ -1302,7 +1304,7 @@
       <c r="Q13" s="1"/>
       <c r="R13" s="1"/>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>12351</v>
       </c>
@@ -1335,7 +1337,7 @@
       <c r="Q14" s="1"/>
       <c r="R14" s="1"/>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>12317</v>
       </c>
@@ -1368,7 +1370,7 @@
       <c r="Q15" s="1"/>
       <c r="R15" s="1"/>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>12374</v>
       </c>
@@ -1401,7 +1403,7 @@
       <c r="Q16" s="1"/>
       <c r="R16" s="1"/>
     </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>12375</v>
       </c>
@@ -1434,7 +1436,7 @@
       <c r="Q17" s="1"/>
       <c r="R17" s="1"/>
     </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>12310</v>
       </c>
@@ -1467,7 +1469,7 @@
       <c r="Q18" s="1"/>
       <c r="R18" s="1"/>
     </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>12309</v>
       </c>
@@ -1500,7 +1502,7 @@
       <c r="Q19" s="1"/>
       <c r="R19" s="1"/>
     </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>12319</v>
       </c>
@@ -1533,7 +1535,7 @@
       <c r="Q20" s="1"/>
       <c r="R20" s="1"/>
     </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>12323</v>
       </c>
@@ -1566,7 +1568,7 @@
       <c r="Q21" s="1"/>
       <c r="R21" s="1"/>
     </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>12414</v>
       </c>
@@ -1599,7 +1601,7 @@
       <c r="Q22" s="1"/>
       <c r="R22" s="1"/>
     </row>
-    <row r="23" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A23" s="2">
         <v>12440</v>
       </c>
@@ -1636,7 +1638,7 @@
         <v>114000</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A24" s="2">
         <v>12610</v>
       </c>
@@ -1673,7 +1675,7 @@
         <v>228000</v>
       </c>
     </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>12644</v>
       </c>
@@ -1706,7 +1708,7 @@
       <c r="Q25" s="1"/>
       <c r="R25" s="1"/>
     </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>12704</v>
       </c>
@@ -1739,7 +1741,7 @@
       <c r="Q26" s="1"/>
       <c r="R26" s="1"/>
     </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>12762</v>
       </c>
@@ -1772,7 +1774,7 @@
       <c r="Q27" s="1"/>
       <c r="R27" s="1"/>
     </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>12779</v>
       </c>
@@ -1805,7 +1807,7 @@
       <c r="Q28" s="1"/>
       <c r="R28" s="1"/>
     </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>12793</v>
       </c>
@@ -1838,7 +1840,7 @@
       <c r="Q29" s="1"/>
       <c r="R29" s="1"/>
     </row>
-    <row r="30" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>12743</v>
       </c>
@@ -1871,7 +1873,7 @@
       <c r="Q30" s="1"/>
       <c r="R30" s="1"/>
     </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>12783</v>
       </c>
@@ -1904,7 +1906,7 @@
       <c r="Q31" s="1"/>
       <c r="R31" s="1"/>
     </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>12867</v>
       </c>
@@ -1937,7 +1939,7 @@
       <c r="Q32" s="1"/>
       <c r="R32" s="1"/>
     </row>
-    <row r="33" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>12046</v>
       </c>
@@ -1972,7 +1974,7 @@
       <c r="Q33" s="1"/>
       <c r="R33" s="1"/>
     </row>
-    <row r="34" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A34" s="2">
         <v>12032</v>
       </c>
@@ -2011,7 +2013,7 @@
         <v>190000</v>
       </c>
     </row>
-    <row r="35" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A35" s="2">
         <v>12033</v>
       </c>
@@ -2048,7 +2050,7 @@
         <v>95000</v>
       </c>
     </row>
-    <row r="36" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A36" s="2">
         <v>12050</v>
       </c>
@@ -2085,7 +2087,7 @@
         <v>285000</v>
       </c>
     </row>
-    <row r="37" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>12040</v>
       </c>
@@ -2118,7 +2120,7 @@
       <c r="Q37" s="1"/>
       <c r="R37" s="1"/>
     </row>
-    <row r="38" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>12119</v>
       </c>
@@ -2151,7 +2153,7 @@
       <c r="Q38" s="1"/>
       <c r="R38" s="1"/>
     </row>
-    <row r="39" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>12045</v>
       </c>
@@ -2184,7 +2186,7 @@
       <c r="Q39" s="1"/>
       <c r="R39" s="1"/>
     </row>
-    <row r="40" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>12132</v>
       </c>
@@ -2217,7 +2219,7 @@
       <c r="Q40" s="1"/>
       <c r="R40" s="1"/>
     </row>
-    <row r="41" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>12164</v>
       </c>
@@ -2250,7 +2252,7 @@
       <c r="Q41" s="1"/>
       <c r="R41" s="1"/>
     </row>
-    <row r="42" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>12170</v>
       </c>
@@ -2283,7 +2285,7 @@
       <c r="Q42" s="1"/>
       <c r="R42" s="1"/>
     </row>
-    <row r="43" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>12153</v>
       </c>
@@ -2316,7 +2318,7 @@
       <c r="Q43" s="1"/>
       <c r="R43" s="1"/>
     </row>
-    <row r="44" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>12173</v>
       </c>
@@ -2349,7 +2351,7 @@
       <c r="Q44" s="1"/>
       <c r="R44" s="1"/>
     </row>
-    <row r="45" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>12167</v>
       </c>
@@ -2382,7 +2384,7 @@
       <c r="Q45" s="1"/>
       <c r="R45" s="1"/>
     </row>
-    <row r="46" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>12168</v>
       </c>
@@ -2415,7 +2417,7 @@
       <c r="Q46" s="1"/>
       <c r="R46" s="1"/>
     </row>
-    <row r="47" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>12204</v>
       </c>
@@ -2450,7 +2452,7 @@
       <c r="Q47" s="1"/>
       <c r="R47" s="1"/>
     </row>
-    <row r="48" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A48" s="2">
         <v>12210</v>
       </c>
@@ -2487,7 +2489,7 @@
         <v>47500</v>
       </c>
     </row>
-    <row r="49" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A49" s="2">
         <v>12131</v>
       </c>
@@ -2526,7 +2528,7 @@
         <v>47500</v>
       </c>
     </row>
-    <row r="50" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>12244</v>
       </c>
@@ -2561,7 +2563,7 @@
       <c r="Q50" s="1"/>
       <c r="R50" s="1"/>
     </row>
-    <row r="51" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>12245</v>
       </c>
@@ -2594,7 +2596,7 @@
       <c r="Q51" s="1"/>
       <c r="R51" s="1"/>
     </row>
-    <row r="52" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>12201</v>
       </c>
@@ -2627,7 +2629,7 @@
       <c r="Q52" s="1"/>
       <c r="R52" s="1"/>
     </row>
-    <row r="53" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>12384</v>
       </c>
@@ -2660,7 +2662,7 @@
       <c r="Q53" s="1"/>
       <c r="R53" s="1"/>
     </row>
-    <row r="54" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>12241</v>
       </c>
@@ -2693,7 +2695,7 @@
       <c r="Q54" s="1"/>
       <c r="R54" s="1"/>
     </row>
-    <row r="55" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A55" s="2">
         <v>12263</v>
       </c>
@@ -2732,7 +2734,7 @@
         <v>380000</v>
       </c>
     </row>
-    <row r="56" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>12392</v>
       </c>
@@ -2765,7 +2767,7 @@
       <c r="Q56" s="1"/>
       <c r="R56" s="1"/>
     </row>
-    <row r="57" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A57" s="2">
         <v>12246</v>
       </c>
@@ -2804,7 +2806,7 @@
         <v>570000</v>
       </c>
     </row>
-    <row r="58" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>12251</v>
       </c>
@@ -2837,7 +2839,7 @@
       <c r="Q58" s="1"/>
       <c r="R58" s="1"/>
     </row>
-    <row r="59" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>12253</v>
       </c>
@@ -2870,7 +2872,7 @@
       <c r="Q59" s="1"/>
       <c r="R59" s="1"/>
     </row>
-    <row r="60" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>12304</v>
       </c>
@@ -2903,7 +2905,7 @@
       <c r="Q60" s="1"/>
       <c r="R60" s="1"/>
     </row>
-    <row r="61" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A61" s="2">
         <v>12354</v>
       </c>
@@ -2940,7 +2942,7 @@
         <v>380000</v>
       </c>
     </row>
-    <row r="62" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>12284</v>
       </c>
@@ -2973,7 +2975,7 @@
       <c r="Q62" s="1"/>
       <c r="R62" s="1"/>
     </row>
-    <row r="63" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>12373</v>
       </c>
@@ -3006,7 +3008,7 @@
       <c r="Q63" s="1"/>
       <c r="R63" s="1"/>
     </row>
-    <row r="64" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>12313</v>
       </c>
@@ -3039,7 +3041,7 @@
       <c r="Q64" s="1"/>
       <c r="R64" s="1"/>
     </row>
-    <row r="65" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>12311</v>
       </c>
@@ -3072,7 +3074,7 @@
       <c r="Q65" s="1"/>
       <c r="R65" s="1"/>
     </row>
-    <row r="66" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>12295</v>
       </c>
@@ -3105,7 +3107,7 @@
       <c r="Q66" s="1"/>
       <c r="R66" s="1"/>
     </row>
-    <row r="67" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>12388</v>
       </c>
@@ -3138,7 +3140,7 @@
       <c r="Q67" s="1"/>
       <c r="R67" s="1"/>
     </row>
-    <row r="68" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>12305</v>
       </c>
@@ -3171,7 +3173,7 @@
       <c r="Q68" s="1"/>
       <c r="R68" s="1"/>
     </row>
-    <row r="69" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A69">
         <v>12116</v>
       </c>
@@ -3204,7 +3206,7 @@
       <c r="Q69" s="1"/>
       <c r="R69" s="1"/>
     </row>
-    <row r="70" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>12415</v>
       </c>
@@ -3237,7 +3239,7 @@
       <c r="Q70" s="1"/>
       <c r="R70" s="1"/>
     </row>
-    <row r="71" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A71">
         <v>12417</v>
       </c>
@@ -3270,7 +3272,7 @@
       <c r="Q71" s="1"/>
       <c r="R71" s="1"/>
     </row>
-    <row r="72" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A72">
         <v>12338</v>
       </c>
@@ -3303,7 +3305,7 @@
       <c r="Q72" s="1"/>
       <c r="R72" s="1"/>
     </row>
-    <row r="73" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A73" s="2">
         <v>12007</v>
       </c>
@@ -3340,7 +3342,7 @@
         <v>760000</v>
       </c>
     </row>
-    <row r="74" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A74">
         <v>12442</v>
       </c>
@@ -3373,7 +3375,7 @@
       <c r="Q74" s="1"/>
       <c r="R74" s="1"/>
     </row>
-    <row r="75" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A75" s="2">
         <v>12427</v>
       </c>
@@ -3410,7 +3412,7 @@
         <v>95000</v>
       </c>
     </row>
-    <row r="76" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A76">
         <v>12425</v>
       </c>
@@ -3443,7 +3445,7 @@
       <c r="Q76" s="1"/>
       <c r="R76" s="1"/>
     </row>
-    <row r="77" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A77">
         <v>12608</v>
       </c>
@@ -3476,7 +3478,7 @@
       <c r="Q77" s="1"/>
       <c r="R77" s="1"/>
     </row>
-    <row r="78" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A78">
         <v>12609</v>
       </c>
@@ -3509,7 +3511,7 @@
       <c r="Q78" s="1"/>
       <c r="R78" s="1"/>
     </row>
-    <row r="79" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A79">
         <v>12611</v>
       </c>
@@ -3544,7 +3546,7 @@
       <c r="Q79" s="1"/>
       <c r="R79" s="1"/>
     </row>
-    <row r="80" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A80">
         <v>12279</v>
       </c>
@@ -3577,7 +3579,7 @@
       <c r="Q80" s="1"/>
       <c r="R80" s="1"/>
     </row>
-    <row r="81" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A81">
         <v>12462</v>
       </c>
@@ -3610,7 +3612,7 @@
       <c r="Q81" s="1"/>
       <c r="R81" s="1"/>
     </row>
-    <row r="82" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A82">
         <v>12474</v>
       </c>
@@ -3643,7 +3645,7 @@
       <c r="Q82" s="1"/>
       <c r="R82" s="1"/>
     </row>
-    <row r="83" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A83">
         <v>12475</v>
       </c>
@@ -3676,7 +3678,7 @@
       <c r="Q83" s="1"/>
       <c r="R83" s="1"/>
     </row>
-    <row r="84" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A84" s="2">
         <v>12695</v>
       </c>
@@ -3715,7 +3717,7 @@
         <v>380000</v>
       </c>
     </row>
-    <row r="85" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A85">
         <v>12694</v>
       </c>
@@ -3748,7 +3750,7 @@
       <c r="Q85" s="1"/>
       <c r="R85" s="1"/>
     </row>
-    <row r="86" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A86">
         <v>12614</v>
       </c>
@@ -3781,7 +3783,7 @@
       <c r="Q86" s="1"/>
       <c r="R86" s="1"/>
     </row>
-    <row r="87" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A87" s="2">
         <v>12993</v>
       </c>
@@ -3822,7 +3824,7 @@
         <v>285000</v>
       </c>
     </row>
-    <row r="88" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A88">
         <v>12411</v>
       </c>
@@ -3855,7 +3857,7 @@
       <c r="Q88" s="1"/>
       <c r="R88" s="1"/>
     </row>
-    <row r="89" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A89">
         <v>12382</v>
       </c>
@@ -3888,7 +3890,7 @@
       <c r="Q89" s="1"/>
       <c r="R89" s="1"/>
     </row>
-    <row r="90" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A90">
         <v>12784</v>
       </c>
@@ -3921,7 +3923,7 @@
       <c r="Q90" s="1"/>
       <c r="R90" s="1"/>
     </row>
-    <row r="91" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A91">
         <v>12785</v>
       </c>
@@ -3954,7 +3956,7 @@
       <c r="Q91" s="1"/>
       <c r="R91" s="1"/>
     </row>
-    <row r="92" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A92">
         <v>12980</v>
       </c>
@@ -3987,7 +3989,7 @@
       <c r="Q92" s="1"/>
       <c r="R92" s="1"/>
     </row>
-    <row r="93" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A93" s="2">
         <v>12773</v>
       </c>
@@ -4024,7 +4026,7 @@
         <v>57000</v>
       </c>
     </row>
-    <row r="94" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A94" s="2">
         <v>12774</v>
       </c>
@@ -4061,7 +4063,7 @@
         <v>57000</v>
       </c>
     </row>
-    <row r="95" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A95" s="2">
         <v>12771</v>
       </c>
@@ -4098,7 +4100,7 @@
         <v>72000</v>
       </c>
     </row>
-    <row r="96" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A96" s="2">
         <v>12772</v>
       </c>
@@ -4137,7 +4139,7 @@
         <v>72000</v>
       </c>
     </row>
-    <row r="97" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A97">
         <v>12741</v>
       </c>
@@ -4170,7 +4172,7 @@
       <c r="Q97" s="1"/>
       <c r="R97" s="1"/>
     </row>
-    <row r="98" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A98">
         <v>12781</v>
       </c>
@@ -4205,7 +4207,7 @@
       <c r="Q98" s="1"/>
       <c r="R98" s="1"/>
     </row>
-    <row r="99" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A99">
         <v>12780</v>
       </c>
@@ -4238,7 +4240,7 @@
       <c r="Q99" s="1"/>
       <c r="R99" s="1"/>
     </row>
-    <row r="100" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A100">
         <v>12808</v>
       </c>
@@ -4271,7 +4273,7 @@
       <c r="Q100" s="1"/>
       <c r="R100" s="1"/>
     </row>
-    <row r="101" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A101" s="2">
         <v>12817</v>
       </c>
@@ -4308,7 +4310,7 @@
         <v>285000</v>
       </c>
     </row>
-    <row r="102" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A102" s="2">
         <v>12818</v>
       </c>
@@ -4345,7 +4347,7 @@
         <v>380000</v>
       </c>
     </row>
-    <row r="103" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A103">
         <v>12819</v>
       </c>
@@ -4378,7 +4380,7 @@
       <c r="Q103" s="1"/>
       <c r="R103" s="1"/>
     </row>
-    <row r="104" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A104" s="2">
         <v>12830</v>
       </c>
@@ -4417,7 +4419,7 @@
         <v>285000</v>
       </c>
     </row>
-    <row r="105" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A105">
         <v>12828</v>
       </c>
@@ -4450,7 +4452,7 @@
       <c r="Q105" s="1"/>
       <c r="R105" s="1"/>
     </row>
-    <row r="106" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A106" s="2">
         <v>12832</v>
       </c>
@@ -4487,7 +4489,7 @@
         <v>285000</v>
       </c>
     </row>
-    <row r="107" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A107" s="2">
         <v>12838</v>
       </c>
@@ -4524,7 +4526,7 @@
         <v>760000</v>
       </c>
     </row>
-    <row r="108" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A108" s="2">
         <v>12979</v>
       </c>
@@ -4561,7 +4563,7 @@
         <v>760000</v>
       </c>
     </row>
-    <row r="109" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A109">
         <v>12825</v>
       </c>
@@ -4594,7 +4596,7 @@
       <c r="Q109" s="1"/>
       <c r="R109" s="1"/>
     </row>
-    <row r="110" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A110">
         <v>12859</v>
       </c>
@@ -4627,7 +4629,7 @@
       <c r="Q110" s="1"/>
       <c r="R110" s="1"/>
     </row>
-    <row r="111" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A111">
         <v>12837</v>
       </c>
@@ -4660,7 +4662,7 @@
       <c r="Q111" s="1"/>
       <c r="R111" s="1"/>
     </row>
-    <row r="112" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:18" x14ac:dyDescent="0.3">
       <c r="C112" t="s">
         <v>6</v>
       </c>
@@ -4704,7 +4706,7 @@
         <v>9862520</v>
       </c>
     </row>
-    <row r="114" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A114" s="2">
         <v>12356</v>
       </c>
@@ -4721,7 +4723,7 @@
         <v>380000</v>
       </c>
     </row>
-    <row r="115" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A115" s="2">
         <v>12872</v>
       </c>
@@ -4738,7 +4740,7 @@
         <v>285000</v>
       </c>
     </row>
-    <row r="116" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A116" s="2">
         <v>12871</v>
       </c>
